--- a/artfynd/A 18024-2026 artfynd.xlsx
+++ b/artfynd/A 18024-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115027970</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -803,12 +798,7 @@
         <v>115027969</v>
       </c>
       <c r="B3" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
